--- a/data/processed/harmonization/Carbon__Soil_organic_carbon_stock/harmonized.xlsx
+++ b/data/processed/harmonization/Carbon__Soil_organic_carbon_stock/harmonized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>187946:0-20</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>187947:20-40</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>187948:40-60</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>187949:60-100</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>187950:0-20</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>188051:20-40</t>
+          <t>20-40:188051</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>187951:40-60</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>187952:60-100</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>187955:0-20</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>187956:20-40</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>187957:40-60</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>188054:60-100</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>187953:0-20</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>187954:20-40</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>188052:40-60</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>188053:60-100</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>187946:0-20</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>187947:20-40</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>187948:40-60</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>187949:60-100</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>187950:0-20</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>188051:20-40</t>
+          <t>20-40:188051</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>187951:40-60</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>187952:60-100</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>187955:0-20</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>187956:20-40</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>187957:40-60</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>188054:60-100</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>187953:0-20</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>187954:20-40</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>188052:40-60</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>188053:60-100</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -25677,12 +25677,12 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Summit:50</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
@@ -25708,7 +25708,7 @@
       <c r="K499" s="2" t="inlineStr"/>
       <c r="L499" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -25725,12 +25725,12 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Shoulder:50</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -25756,7 +25756,7 @@
       <c r="K500" s="2" t="inlineStr"/>
       <c r="L500" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -25773,12 +25773,12 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Upper Backslope:50</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
@@ -25804,7 +25804,7 @@
       <c r="K501" s="2" t="inlineStr"/>
       <c r="L501" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -25821,12 +25821,12 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Lower Backslope:50</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
@@ -25852,7 +25852,7 @@
       <c r="K502" s="2" t="inlineStr"/>
       <c r="L502" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -25869,12 +25869,12 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Footslope:50</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
@@ -25900,7 +25900,7 @@
       <c r="K503" s="2" t="inlineStr"/>
       <c r="L503" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -25917,12 +25917,12 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Toeslope:50</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -25948,7 +25948,7 @@
       <c r="K504" s="2" t="inlineStr"/>
       <c r="L504" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -25965,12 +25965,12 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:50</t>
+          <t>Happy Valley:Basin:50</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -25996,7 +25996,7 @@
       <c r="K505" s="2" t="inlineStr"/>
       <c r="L505" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26013,12 +26013,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Summit:50</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -26044,7 +26044,7 @@
       <c r="K506" s="2" t="inlineStr"/>
       <c r="L506" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26061,12 +26061,12 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Shoulder:50</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
@@ -26092,7 +26092,7 @@
       <c r="K507" s="2" t="inlineStr"/>
       <c r="L507" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26109,12 +26109,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Upper Backslope:50</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -26140,7 +26140,7 @@
       <c r="K508" s="2" t="inlineStr"/>
       <c r="L508" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26157,12 +26157,12 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Lower Backslope:50</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -26188,7 +26188,7 @@
       <c r="K509" s="2" t="inlineStr"/>
       <c r="L509" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26205,12 +26205,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Footslope:50</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -26236,7 +26236,7 @@
       <c r="K510" s="2" t="inlineStr"/>
       <c r="L510" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26253,12 +26253,12 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Toeslope:50</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -26284,7 +26284,7 @@
       <c r="K511" s="2" t="inlineStr"/>
       <c r="L511" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26301,12 +26301,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:50</t>
+          <t>Sagwon Hills:Basin:50</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -26332,7 +26332,7 @@
       <c r="K512" s="2" t="inlineStr"/>
       <c r="L512" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26349,12 +26349,12 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Summit:100</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
@@ -26380,7 +26380,7 @@
       <c r="K513" s="2" t="inlineStr"/>
       <c r="L513" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26397,12 +26397,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Shoulder:100</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -26428,7 +26428,7 @@
       <c r="K514" s="2" t="inlineStr"/>
       <c r="L514" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26445,12 +26445,12 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Upper Backslope:100</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
@@ -26476,7 +26476,7 @@
       <c r="K515" s="2" t="inlineStr"/>
       <c r="L515" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26493,12 +26493,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Lower Backslope:100</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -26524,7 +26524,7 @@
       <c r="K516" s="2" t="inlineStr"/>
       <c r="L516" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26541,12 +26541,12 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Footslope:100</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
@@ -26572,7 +26572,7 @@
       <c r="K517" s="2" t="inlineStr"/>
       <c r="L517" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26589,12 +26589,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Toeslope:100</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -26620,7 +26620,7 @@
       <c r="K518" s="2" t="inlineStr"/>
       <c r="L518" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26637,12 +26637,12 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:100</t>
+          <t>Happy Valley:Basin:100</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -26668,7 +26668,7 @@
       <c r="K519" s="2" t="inlineStr"/>
       <c r="L519" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26685,12 +26685,12 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Summit:100</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
@@ -26716,7 +26716,7 @@
       <c r="K520" s="2" t="inlineStr"/>
       <c r="L520" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26733,12 +26733,12 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Shoulder:100</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
@@ -26764,7 +26764,7 @@
       <c r="K521" s="2" t="inlineStr"/>
       <c r="L521" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26781,12 +26781,12 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Upper Backslope:100</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
@@ -26812,7 +26812,7 @@
       <c r="K522" s="2" t="inlineStr"/>
       <c r="L522" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26829,12 +26829,12 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Lower Backslope:100</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
@@ -26860,7 +26860,7 @@
       <c r="K523" s="2" t="inlineStr"/>
       <c r="L523" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26877,12 +26877,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Footslope:100</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -26908,7 +26908,7 @@
       <c r="K524" s="2" t="inlineStr"/>
       <c r="L524" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26925,12 +26925,12 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Toeslope:100</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
@@ -26956,7 +26956,7 @@
       <c r="K525" s="2" t="inlineStr"/>
       <c r="L525" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -26973,12 +26973,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:100</t>
+          <t>Sagwon Hills:Basin:100</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -27004,7 +27004,7 @@
       <c r="K526" s="2" t="inlineStr"/>
       <c r="L526" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27021,12 +27021,12 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:150</t>
+          <t>Happy Valley:Lower Backslope:150</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
@@ -27052,7 +27052,7 @@
       <c r="K527" s="2" t="inlineStr"/>
       <c r="L527" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27069,12 +27069,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:150</t>
+          <t>Happy Valley:Footslope:150</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
@@ -27100,7 +27100,7 @@
       <c r="K528" s="2" t="inlineStr"/>
       <c r="L528" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27117,12 +27117,12 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:150</t>
+          <t>Happy Valley:Toeslope:150</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
@@ -27148,7 +27148,7 @@
       <c r="K529" s="2" t="inlineStr"/>
       <c r="L529" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27165,12 +27165,12 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:150</t>
+          <t>Happy Valley:Basin:150</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
@@ -27196,7 +27196,7 @@
       <c r="K530" s="2" t="inlineStr"/>
       <c r="L530" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27213,12 +27213,12 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Summit:150</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
@@ -27244,7 +27244,7 @@
       <c r="K531" s="2" t="inlineStr"/>
       <c r="L531" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27261,12 +27261,12 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Shoulder:150</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
@@ -27292,7 +27292,7 @@
       <c r="K532" s="2" t="inlineStr"/>
       <c r="L532" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27309,12 +27309,12 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Lower Backslope:150</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
@@ -27340,7 +27340,7 @@
       <c r="K533" s="2" t="inlineStr"/>
       <c r="L533" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27357,12 +27357,12 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Footslope:150</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
@@ -27388,7 +27388,7 @@
       <c r="K534" s="2" t="inlineStr"/>
       <c r="L534" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27405,12 +27405,12 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Toeslope:150</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
@@ -27436,7 +27436,7 @@
       <c r="K535" s="2" t="inlineStr"/>
       <c r="L535" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27453,12 +27453,12 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:150</t>
+          <t>Sagwon Hills:Basin:150</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
@@ -27484,7 +27484,7 @@
       <c r="K536" s="2" t="inlineStr"/>
       <c r="L536" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27501,12 +27501,12 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:200</t>
+          <t>Happy Valley:Lower Backslope:200</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
@@ -27532,7 +27532,7 @@
       <c r="K537" s="2" t="inlineStr"/>
       <c r="L537" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27549,12 +27549,12 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:200</t>
+          <t>Happy Valley:Footslope:200</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
@@ -27580,7 +27580,7 @@
       <c r="K538" s="2" t="inlineStr"/>
       <c r="L538" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27597,12 +27597,12 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:200</t>
+          <t>Happy Valley:Toeslope:200</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
@@ -27628,7 +27628,7 @@
       <c r="K539" s="2" t="inlineStr"/>
       <c r="L539" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27645,12 +27645,12 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley:200</t>
+          <t>Happy Valley:Basin:200</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
@@ -27676,7 +27676,7 @@
       <c r="K540" s="2" t="inlineStr"/>
       <c r="L540" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27693,12 +27693,12 @@
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:200</t>
+          <t>Sagwon Hills:Basin:200</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr">
@@ -27724,7 +27724,7 @@
       <c r="K541" s="2" t="inlineStr"/>
       <c r="L541" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
@@ -27741,12 +27741,12 @@
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>Sagwon Hills:300</t>
+          <t>Sagwon Hills:Basin:300</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>location:depth</t>
+          <t>location:hillslope_position:depth</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
@@ -27772,7 +27772,7 @@
       <c r="K542" s="2" t="inlineStr"/>
       <c r="L542" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm; id not unique: 42 rows share an id</t>
+          <t>lat/long source: doi:10.15485/2407117:stocks_by_core.csv (joined on location); data key location; source column c_stocks_kgC_m-2 (kg-C/m^2, unit from data dictionary); depth from depth_cm</t>
         </is>
       </c>
     </row>
